--- a/Robotové skříně.xlsx
+++ b/Robotové skříně.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FG8MXQ0.SKODA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FG8MXQ0.SKODA\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D7B53BE-2021-4894-BC88-F752DCE40AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9718C1BB-E1DF-402D-87C4-B1C1222DFF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C83A040F-E645-4B4B-9049-20FF3501B811}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{745ABB97-1670-4432-867B-93A03AD5411C}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="1384">
   <si>
     <t>Vybavení</t>
   </si>
@@ -2861,6 +2861,9 @@
     <t>Rám vnější pravý 38x - St. 3815 - robot R01</t>
   </si>
   <si>
+    <t>Rám vnější pravý 38x - St. 3815 - robot R02</t>
+  </si>
+  <si>
     <t>Rám vnější pravý 38x - St. 3820 - robot R01</t>
   </si>
   <si>
@@ -3353,6 +3356,9 @@
     <t>Rám vnější pravý 316 - St. 3730 - robot R01</t>
   </si>
   <si>
+    <t>Střecha - St. 4940 - robot R01</t>
+  </si>
+  <si>
     <t>Střecha - St. 4820 - robot R01</t>
   </si>
   <si>
@@ -3389,9 +3395,6 @@
     <t>Střecha - St. 4930 - robot R01</t>
   </si>
   <si>
-    <t>Střecha - St. 4940 - robot R01</t>
-  </si>
-  <si>
     <t>Střecha 2 - St. 4820 - robot R01</t>
   </si>
   <si>
@@ -4182,6 +4185,9 @@
   </si>
   <si>
     <t>Tréninková buňka - St. 9030 - robot R01</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -4552,8 +4558,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{909F91A0-4334-4C3D-8855-903AE8B57442}">
-  <dimension ref="A1:B1383"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F234B883-AEAE-48CB-A8F0-A72DAC27E1E7}">
+  <dimension ref="A1:B1384"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -12084,7 +12090,7 @@
         <v>9122977</v>
       </c>
       <c r="B941" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.2">
@@ -12092,7 +12098,7 @@
         <v>10089911</v>
       </c>
       <c r="B942" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.2">
@@ -12100,7 +12106,7 @@
         <v>10089959</v>
       </c>
       <c r="B943" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.2">
@@ -12108,7 +12114,7 @@
         <v>10090039</v>
       </c>
       <c r="B944" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.2">
@@ -12116,7 +12122,7 @@
         <v>10090218</v>
       </c>
       <c r="B945" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.2">
@@ -12124,7 +12130,7 @@
         <v>10090242</v>
       </c>
       <c r="B946" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.2">
@@ -12132,7 +12138,7 @@
         <v>10090255</v>
       </c>
       <c r="B947" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.2">
@@ -12140,7 +12146,7 @@
         <v>10090311</v>
       </c>
       <c r="B948" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.2">
@@ -12148,7 +12154,7 @@
         <v>10090459</v>
       </c>
       <c r="B949" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.2">
@@ -12156,7 +12162,7 @@
         <v>10090604</v>
       </c>
       <c r="B950" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.2">
@@ -12164,7 +12170,7 @@
         <v>10090612</v>
       </c>
       <c r="B951" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.2">
@@ -12172,7 +12178,7 @@
         <v>10241249</v>
       </c>
       <c r="B952" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.2">
@@ -12180,7 +12186,7 @@
         <v>10241688</v>
       </c>
       <c r="B953" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.2">
@@ -12188,7 +12194,7 @@
         <v>10090628</v>
       </c>
       <c r="B954" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.2">
@@ -12196,7 +12202,7 @@
         <v>10090675</v>
       </c>
       <c r="B955" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.2">
@@ -12204,7 +12210,7 @@
         <v>10090685</v>
       </c>
       <c r="B956" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.2">
@@ -12212,7 +12218,7 @@
         <v>10090763</v>
       </c>
       <c r="B957" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.2">
@@ -12220,7 +12226,7 @@
         <v>10141044</v>
       </c>
       <c r="B958" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.2">
@@ -12228,7 +12234,7 @@
         <v>10141181</v>
       </c>
       <c r="B959" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.2">
@@ -12236,7 +12242,7 @@
         <v>10141186</v>
       </c>
       <c r="B960" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.2">
@@ -12244,7 +12250,7 @@
         <v>10211120</v>
       </c>
       <c r="B961" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.2">
@@ -12252,7 +12258,7 @@
         <v>10211124</v>
       </c>
       <c r="B962" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.2">
@@ -12260,7 +12266,7 @@
         <v>10182234</v>
       </c>
       <c r="B963" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.2">
@@ -12268,7 +12274,7 @@
         <v>10182237</v>
       </c>
       <c r="B964" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.2">
@@ -12276,7 +12282,7 @@
         <v>10211184</v>
       </c>
       <c r="B965" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.2">
@@ -12284,7 +12290,7 @@
         <v>10211196</v>
       </c>
       <c r="B966" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.2">
@@ -12292,7 +12298,7 @@
         <v>10141256</v>
       </c>
       <c r="B967" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.2">
@@ -12300,7 +12306,7 @@
         <v>10141372</v>
       </c>
       <c r="B968" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.2">
@@ -12308,7 +12314,7 @@
         <v>10141377</v>
       </c>
       <c r="B969" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.2">
@@ -12316,7 +12322,7 @@
         <v>10182239</v>
       </c>
       <c r="B970" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.2">
@@ -12324,7 +12330,7 @@
         <v>10141221</v>
       </c>
       <c r="B971" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.2">
@@ -12332,7 +12338,7 @@
         <v>10141403</v>
       </c>
       <c r="B972" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.2">
@@ -12340,7 +12346,7 @@
         <v>9087665</v>
       </c>
       <c r="B973" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.2">
@@ -12348,7 +12354,7 @@
         <v>10141467</v>
       </c>
       <c r="B974" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.2">
@@ -12356,7 +12362,7 @@
         <v>10141652</v>
       </c>
       <c r="B975" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.2">
@@ -12364,7 +12370,7 @@
         <v>10141657</v>
       </c>
       <c r="B976" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.2">
@@ -12372,7 +12378,7 @@
         <v>10141662</v>
       </c>
       <c r="B977" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.2">
@@ -12380,7 +12386,7 @@
         <v>9070362</v>
       </c>
       <c r="B978" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.2">
@@ -12388,7 +12394,7 @@
         <v>9070368</v>
       </c>
       <c r="B979" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.2">
@@ -12396,7 +12402,7 @@
         <v>10141667</v>
       </c>
       <c r="B980" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.2">
@@ -12404,7 +12410,7 @@
         <v>9070155</v>
       </c>
       <c r="B981" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.2">
@@ -12412,7 +12418,7 @@
         <v>9070168</v>
       </c>
       <c r="B982" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.2">
@@ -12420,7 +12426,7 @@
         <v>10182385</v>
       </c>
       <c r="B983" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.2">
@@ -12428,7 +12434,7 @@
         <v>10182394</v>
       </c>
       <c r="B984" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.2">
@@ -12436,7 +12442,7 @@
         <v>10141720</v>
       </c>
       <c r="B985" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.2">
@@ -12444,7 +12450,7 @@
         <v>9092169</v>
       </c>
       <c r="B986" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.2">
@@ -12452,7 +12458,7 @@
         <v>9101449</v>
       </c>
       <c r="B987" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.2">
@@ -12460,7 +12466,7 @@
         <v>9101456</v>
       </c>
       <c r="B988" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.2">
@@ -12468,7 +12474,7 @@
         <v>10141790</v>
       </c>
       <c r="B989" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.2">
@@ -12476,7 +12482,7 @@
         <v>10141924</v>
       </c>
       <c r="B990" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.2">
@@ -12484,7 +12490,7 @@
         <v>10141929</v>
       </c>
       <c r="B991" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.2">
@@ -12492,7 +12498,7 @@
         <v>10141934</v>
       </c>
       <c r="B992" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.2">
@@ -12500,7 +12506,7 @@
         <v>9063075</v>
       </c>
       <c r="B993" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.2">
@@ -12508,7 +12514,7 @@
         <v>10141939</v>
       </c>
       <c r="B994" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.2">
@@ -12516,7 +12522,7 @@
         <v>9063116</v>
       </c>
       <c r="B995" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.2">
@@ -12524,7 +12530,7 @@
         <v>9063123</v>
       </c>
       <c r="B996" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.2">
@@ -12532,7 +12538,7 @@
         <v>9063130</v>
       </c>
       <c r="B997" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.2">
@@ -12540,7 +12546,7 @@
         <v>9063137</v>
       </c>
       <c r="B998" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.2">
@@ -12548,7 +12554,7 @@
         <v>9063145</v>
       </c>
       <c r="B999" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.2">
@@ -12556,7 +12562,7 @@
         <v>10141995</v>
       </c>
       <c r="B1000" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.2">
@@ -12564,7 +12570,7 @@
         <v>10142000</v>
       </c>
       <c r="B1001" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1002" spans="1:2" x14ac:dyDescent="0.2">
@@ -12572,7 +12578,7 @@
         <v>10142005</v>
       </c>
       <c r="B1002" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1003" spans="1:2" x14ac:dyDescent="0.2">
@@ -12580,7 +12586,7 @@
         <v>10142010</v>
       </c>
       <c r="B1003" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="1004" spans="1:2" x14ac:dyDescent="0.2">
@@ -12588,7 +12594,7 @@
         <v>10142232</v>
       </c>
       <c r="B1004" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1005" spans="1:2" x14ac:dyDescent="0.2">
@@ -12596,7 +12602,7 @@
         <v>10142374</v>
       </c>
       <c r="B1005" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.2">
@@ -12604,7 +12610,7 @@
         <v>10142379</v>
       </c>
       <c r="B1006" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1007" spans="1:2" x14ac:dyDescent="0.2">
@@ -12612,7 +12618,7 @@
         <v>10211510</v>
       </c>
       <c r="B1007" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1008" spans="1:2" x14ac:dyDescent="0.2">
@@ -12620,7 +12626,7 @@
         <v>10211512</v>
       </c>
       <c r="B1008" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1009" spans="1:2" x14ac:dyDescent="0.2">
@@ -12628,7 +12634,7 @@
         <v>10182254</v>
       </c>
       <c r="B1009" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1010" spans="1:2" x14ac:dyDescent="0.2">
@@ -12636,7 +12642,7 @@
         <v>10182260</v>
       </c>
       <c r="B1010" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="1011" spans="1:2" x14ac:dyDescent="0.2">
@@ -12644,7 +12650,7 @@
         <v>10211529</v>
       </c>
       <c r="B1011" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="1012" spans="1:2" x14ac:dyDescent="0.2">
@@ -12652,7 +12658,7 @@
         <v>10142442</v>
       </c>
       <c r="B1012" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="1013" spans="1:2" x14ac:dyDescent="0.2">
@@ -12660,7 +12666,7 @@
         <v>10182247</v>
       </c>
       <c r="B1013" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1014" spans="1:2" x14ac:dyDescent="0.2">
@@ -12668,7 +12674,7 @@
         <v>10187364</v>
       </c>
       <c r="B1014" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.2">
@@ -12676,7 +12682,7 @@
         <v>10211535</v>
       </c>
       <c r="B1015" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.2">
@@ -12684,7 +12690,7 @@
         <v>10182263</v>
       </c>
       <c r="B1016" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="1017" spans="1:2" x14ac:dyDescent="0.2">
@@ -12692,7 +12698,7 @@
         <v>10142591</v>
       </c>
       <c r="B1017" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="1018" spans="1:2" x14ac:dyDescent="0.2">
@@ -12700,7 +12706,7 @@
         <v>10142596</v>
       </c>
       <c r="B1018" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="1019" spans="1:2" x14ac:dyDescent="0.2">
@@ -12708,7 +12714,7 @@
         <v>10182266</v>
       </c>
       <c r="B1019" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.2">
@@ -12716,7 +12722,7 @@
         <v>10142622</v>
       </c>
       <c r="B1020" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="1021" spans="1:2" x14ac:dyDescent="0.2">
@@ -12724,7 +12730,7 @@
         <v>9087659</v>
       </c>
       <c r="B1021" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="1022" spans="1:2" x14ac:dyDescent="0.2">
@@ -12732,7 +12738,7 @@
         <v>10142685</v>
       </c>
       <c r="B1022" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="1023" spans="1:2" x14ac:dyDescent="0.2">
@@ -12740,7 +12746,7 @@
         <v>10142870</v>
       </c>
       <c r="B1023" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1024" spans="1:2" x14ac:dyDescent="0.2">
@@ -12748,7 +12754,7 @@
         <v>10142875</v>
       </c>
       <c r="B1024" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="1025" spans="1:2" x14ac:dyDescent="0.2">
@@ -12756,7 +12762,7 @@
         <v>10142880</v>
       </c>
       <c r="B1025" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="1026" spans="1:2" x14ac:dyDescent="0.2">
@@ -12764,7 +12770,7 @@
         <v>9070418</v>
       </c>
       <c r="B1026" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.2">
@@ -12772,7 +12778,7 @@
         <v>9070422</v>
       </c>
       <c r="B1027" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="1028" spans="1:2" x14ac:dyDescent="0.2">
@@ -12780,7 +12786,7 @@
         <v>10142885</v>
       </c>
       <c r="B1028" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="1029" spans="1:2" x14ac:dyDescent="0.2">
@@ -12788,7 +12794,7 @@
         <v>9070181</v>
       </c>
       <c r="B1029" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="1030" spans="1:2" x14ac:dyDescent="0.2">
@@ -12796,7 +12802,7 @@
         <v>9070194</v>
       </c>
       <c r="B1030" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1031" spans="1:2" x14ac:dyDescent="0.2">
@@ -12804,7 +12810,7 @@
         <v>10185138</v>
       </c>
       <c r="B1031" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1032" spans="1:2" x14ac:dyDescent="0.2">
@@ -12812,7 +12818,7 @@
         <v>10185152</v>
       </c>
       <c r="B1032" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1033" spans="1:2" x14ac:dyDescent="0.2">
@@ -12820,7 +12826,7 @@
         <v>10185165</v>
       </c>
       <c r="B1033" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1034" spans="1:2" x14ac:dyDescent="0.2">
@@ -12828,7 +12834,7 @@
         <v>10142938</v>
       </c>
       <c r="B1034" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1035" spans="1:2" x14ac:dyDescent="0.2">
@@ -12836,7 +12842,7 @@
         <v>9092556</v>
       </c>
       <c r="B1035" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1036" spans="1:2" x14ac:dyDescent="0.2">
@@ -12844,7 +12850,7 @@
         <v>9101376</v>
       </c>
       <c r="B1036" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.2">
@@ -12852,7 +12858,7 @@
         <v>9101384</v>
       </c>
       <c r="B1037" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="1038" spans="1:2" x14ac:dyDescent="0.2">
@@ -12860,7 +12866,7 @@
         <v>10143008</v>
       </c>
       <c r="B1038" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="1039" spans="1:2" x14ac:dyDescent="0.2">
@@ -12868,7 +12874,7 @@
         <v>10143142</v>
       </c>
       <c r="B1039" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="1040" spans="1:2" x14ac:dyDescent="0.2">
@@ -12876,7 +12882,7 @@
         <v>10143147</v>
       </c>
       <c r="B1040" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="1041" spans="1:2" x14ac:dyDescent="0.2">
@@ -12884,7 +12890,7 @@
         <v>10143152</v>
       </c>
       <c r="B1041" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="1042" spans="1:2" x14ac:dyDescent="0.2">
@@ -12892,7 +12898,7 @@
         <v>9088713</v>
       </c>
       <c r="B1042" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1043" spans="1:2" x14ac:dyDescent="0.2">
@@ -12900,7 +12906,7 @@
         <v>9101832</v>
       </c>
       <c r="B1043" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="1044" spans="1:2" x14ac:dyDescent="0.2">
@@ -12908,7 +12914,7 @@
         <v>9101835</v>
       </c>
       <c r="B1044" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="1045" spans="1:2" x14ac:dyDescent="0.2">
@@ -12916,7 +12922,7 @@
         <v>9101837</v>
       </c>
       <c r="B1045" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="1046" spans="1:2" x14ac:dyDescent="0.2">
@@ -12924,7 +12930,7 @@
         <v>9101841</v>
       </c>
       <c r="B1046" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="1047" spans="1:2" x14ac:dyDescent="0.2">
@@ -12932,7 +12938,7 @@
         <v>9101840</v>
       </c>
       <c r="B1047" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="1048" spans="1:2" x14ac:dyDescent="0.2">
@@ -12940,7 +12946,7 @@
         <v>10143157</v>
       </c>
       <c r="B1048" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="1049" spans="1:2" x14ac:dyDescent="0.2">
@@ -12948,7 +12954,7 @@
         <v>10143213</v>
       </c>
       <c r="B1049" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="1050" spans="1:2" x14ac:dyDescent="0.2">
@@ -12956,7 +12962,7 @@
         <v>10143218</v>
       </c>
       <c r="B1050" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="1051" spans="1:2" x14ac:dyDescent="0.2">
@@ -12964,7 +12970,7 @@
         <v>10143223</v>
       </c>
       <c r="B1051" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="1052" spans="1:2" x14ac:dyDescent="0.2">
@@ -12972,7 +12978,7 @@
         <v>10143228</v>
       </c>
       <c r="B1052" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="1053" spans="1:2" x14ac:dyDescent="0.2">
@@ -12980,7 +12986,7 @@
         <v>9099758</v>
       </c>
       <c r="B1053" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1054" spans="1:2" x14ac:dyDescent="0.2">
@@ -12988,7 +12994,7 @@
         <v>9099786</v>
       </c>
       <c r="B1054" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="1055" spans="1:2" x14ac:dyDescent="0.2">
@@ -12996,7 +13002,7 @@
         <v>9099810</v>
       </c>
       <c r="B1055" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="1056" spans="1:2" x14ac:dyDescent="0.2">
@@ -13004,7 +13010,7 @@
         <v>9099818</v>
       </c>
       <c r="B1056" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="1057" spans="1:2" x14ac:dyDescent="0.2">
@@ -13012,7 +13018,7 @@
         <v>9099826</v>
       </c>
       <c r="B1057" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="1058" spans="1:2" x14ac:dyDescent="0.2">
@@ -13020,7 +13026,7 @@
         <v>10142015</v>
       </c>
       <c r="B1058" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="1059" spans="1:2" x14ac:dyDescent="0.2">
@@ -13028,7 +13034,7 @@
         <v>9043595</v>
       </c>
       <c r="B1059" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="1060" spans="1:2" x14ac:dyDescent="0.2">
@@ -13036,7 +13042,7 @@
         <v>9043619</v>
       </c>
       <c r="B1060" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1061" spans="1:2" x14ac:dyDescent="0.2">
@@ -13044,7 +13050,7 @@
         <v>10143238</v>
       </c>
       <c r="B1061" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="1062" spans="1:2" x14ac:dyDescent="0.2">
@@ -13052,7 +13058,7 @@
         <v>9063201</v>
       </c>
       <c r="B1062" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="1063" spans="1:2" x14ac:dyDescent="0.2">
@@ -13060,7 +13066,7 @@
         <v>9063208</v>
       </c>
       <c r="B1063" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="1064" spans="1:2" x14ac:dyDescent="0.2">
@@ -13068,7 +13074,7 @@
         <v>9063215</v>
       </c>
       <c r="B1064" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="1065" spans="1:2" x14ac:dyDescent="0.2">
@@ -13076,7 +13082,7 @@
         <v>9063222</v>
       </c>
       <c r="B1065" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="1066" spans="1:2" x14ac:dyDescent="0.2">
@@ -13084,7 +13090,7 @@
         <v>9067005</v>
       </c>
       <c r="B1066" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="1067" spans="1:2" x14ac:dyDescent="0.2">
@@ -13092,7 +13098,7 @@
         <v>9043502</v>
       </c>
       <c r="B1067" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="1068" spans="1:2" x14ac:dyDescent="0.2">
@@ -13100,7 +13106,7 @@
         <v>9043526</v>
       </c>
       <c r="B1068" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="1069" spans="1:2" x14ac:dyDescent="0.2">
@@ -13108,7 +13114,7 @@
         <v>9092597</v>
       </c>
       <c r="B1069" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="1070" spans="1:2" x14ac:dyDescent="0.2">
@@ -13116,7 +13122,7 @@
         <v>10159615</v>
       </c>
       <c r="B1070" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="1071" spans="1:2" x14ac:dyDescent="0.2">
@@ -13124,7 +13130,7 @@
         <v>10159700</v>
       </c>
       <c r="B1071" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1072" spans="1:2" x14ac:dyDescent="0.2">
@@ -13132,7 +13138,7 @@
         <v>10159743</v>
       </c>
       <c r="B1072" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="1073" spans="1:2" x14ac:dyDescent="0.2">
@@ -13140,7 +13146,7 @@
         <v>10192204</v>
       </c>
       <c r="B1073" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="1074" spans="1:2" x14ac:dyDescent="0.2">
@@ -13148,7 +13154,7 @@
         <v>10159764</v>
       </c>
       <c r="B1074" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="1075" spans="1:2" x14ac:dyDescent="0.2">
@@ -13156,7 +13162,7 @@
         <v>10159929</v>
       </c>
       <c r="B1075" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1076" spans="1:2" x14ac:dyDescent="0.2">
@@ -13164,7 +13170,7 @@
         <v>10159954</v>
       </c>
       <c r="B1076" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="1077" spans="1:2" x14ac:dyDescent="0.2">
@@ -13172,7 +13178,7 @@
         <v>10159984</v>
       </c>
       <c r="B1077" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="1078" spans="1:2" x14ac:dyDescent="0.2">
@@ -13180,7 +13186,7 @@
         <v>10160119</v>
       </c>
       <c r="B1078" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="1079" spans="1:2" x14ac:dyDescent="0.2">
@@ -13188,7 +13194,7 @@
         <v>10160298</v>
       </c>
       <c r="B1079" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="1080" spans="1:2" x14ac:dyDescent="0.2">
@@ -13196,7 +13202,7 @@
         <v>10160306</v>
       </c>
       <c r="B1080" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1081" spans="1:2" x14ac:dyDescent="0.2">
@@ -13204,7 +13210,7 @@
         <v>10160314</v>
       </c>
       <c r="B1081" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="1082" spans="1:2" x14ac:dyDescent="0.2">
@@ -13212,7 +13218,7 @@
         <v>10160323</v>
       </c>
       <c r="B1082" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="1083" spans="1:2" x14ac:dyDescent="0.2">
@@ -13220,7 +13226,7 @@
         <v>10160363</v>
       </c>
       <c r="B1083" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="1084" spans="1:2" x14ac:dyDescent="0.2">
@@ -13228,7 +13234,7 @@
         <v>9092059</v>
       </c>
       <c r="B1084" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.2">
@@ -13236,7 +13242,7 @@
         <v>10160388</v>
       </c>
       <c r="B1085" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="1086" spans="1:2" x14ac:dyDescent="0.2">
@@ -13244,7 +13250,7 @@
         <v>10160428</v>
       </c>
       <c r="B1086" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.2">
@@ -13252,7 +13258,7 @@
         <v>10143406</v>
       </c>
       <c r="B1087" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="1088" spans="1:2" x14ac:dyDescent="0.2">
@@ -13260,7 +13266,7 @@
         <v>10143414</v>
       </c>
       <c r="B1088" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1089" spans="1:2" x14ac:dyDescent="0.2">
@@ -13268,7 +13274,7 @@
         <v>10143495</v>
       </c>
       <c r="B1089" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="1090" spans="1:2" x14ac:dyDescent="0.2">
@@ -13276,7 +13282,7 @@
         <v>10143517</v>
       </c>
       <c r="B1090" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1091" spans="1:2" x14ac:dyDescent="0.2">
@@ -13284,7 +13290,7 @@
         <v>10143623</v>
       </c>
       <c r="B1091" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="1092" spans="1:2" x14ac:dyDescent="0.2">
@@ -13292,7 +13298,7 @@
         <v>10193285</v>
       </c>
       <c r="B1092" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="1093" spans="1:2" x14ac:dyDescent="0.2">
@@ -13300,7 +13306,7 @@
         <v>10143638</v>
       </c>
       <c r="B1093" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="1094" spans="1:2" x14ac:dyDescent="0.2">
@@ -13308,7 +13314,7 @@
         <v>10143803</v>
       </c>
       <c r="B1094" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1095" spans="1:2" x14ac:dyDescent="0.2">
@@ -13316,7 +13322,7 @@
         <v>10143828</v>
       </c>
       <c r="B1095" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="1096" spans="1:2" x14ac:dyDescent="0.2">
@@ -13324,7 +13330,7 @@
         <v>10143858</v>
       </c>
       <c r="B1096" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1097" spans="1:2" x14ac:dyDescent="0.2">
@@ -13332,7 +13338,7 @@
         <v>10143993</v>
       </c>
       <c r="B1097" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1098" spans="1:2" x14ac:dyDescent="0.2">
@@ -13340,7 +13346,7 @@
         <v>10144172</v>
       </c>
       <c r="B1098" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1099" spans="1:2" x14ac:dyDescent="0.2">
@@ -13348,7 +13354,7 @@
         <v>10144180</v>
       </c>
       <c r="B1099" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="1100" spans="1:2" x14ac:dyDescent="0.2">
@@ -13356,7 +13362,7 @@
         <v>10144188</v>
       </c>
       <c r="B1100" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1101" spans="1:2" x14ac:dyDescent="0.2">
@@ -13364,7 +13370,7 @@
         <v>10144197</v>
       </c>
       <c r="B1101" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="1102" spans="1:2" x14ac:dyDescent="0.2">
@@ -13372,7 +13378,7 @@
         <v>10144236</v>
       </c>
       <c r="B1102" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="1103" spans="1:2" x14ac:dyDescent="0.2">
@@ -13380,7 +13386,7 @@
         <v>9092060</v>
       </c>
       <c r="B1103" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="1104" spans="1:2" x14ac:dyDescent="0.2">
@@ -13388,7 +13394,7 @@
         <v>10144245</v>
       </c>
       <c r="B1104" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="1105" spans="1:2" x14ac:dyDescent="0.2">
@@ -13396,111 +13402,111 @@
         <v>10144283</v>
       </c>
       <c r="B1105" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="1106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1106">
-        <v>10092454</v>
+        <v>10093139</v>
       </c>
       <c r="B1106" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="1107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1107">
-        <v>10092547</v>
+        <v>10092454</v>
       </c>
       <c r="B1107" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="1108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1108">
-        <v>10092626</v>
+        <v>10092547</v>
       </c>
       <c r="B1108" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="1109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1109">
-        <v>10092641</v>
+        <v>10092626</v>
       </c>
       <c r="B1109" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1110">
-        <v>10092773</v>
+        <v>10092641</v>
       </c>
       <c r="B1110" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="1111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1111">
-        <v>10092779</v>
+        <v>10092773</v>
       </c>
       <c r="B1111" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="1112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1112">
-        <v>10092841</v>
+        <v>10092779</v>
       </c>
       <c r="B1112" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="1113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1113">
-        <v>10092856</v>
+        <v>10092841</v>
       </c>
       <c r="B1113" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="1114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1114">
-        <v>10092871</v>
+        <v>10092856</v>
       </c>
       <c r="B1114" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1115">
-        <v>10092958</v>
+        <v>10092871</v>
       </c>
       <c r="B1115" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="1116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1116">
-        <v>10092968</v>
+        <v>10092958</v>
       </c>
       <c r="B1116" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1117">
-        <v>10093133</v>
+        <v>10092968</v>
       </c>
       <c r="B1117" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1118">
-        <v>10093139</v>
+        <v>10093133</v>
       </c>
       <c r="B1118" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="1119" spans="1:2" x14ac:dyDescent="0.2">
@@ -13508,7 +13514,7 @@
         <v>9062176</v>
       </c>
       <c r="B1119" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="1120" spans="1:2" x14ac:dyDescent="0.2">
@@ -13516,7 +13522,7 @@
         <v>9062231</v>
       </c>
       <c r="B1120" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="1121" spans="1:2" x14ac:dyDescent="0.2">
@@ -13524,7 +13530,7 @@
         <v>9062254</v>
       </c>
       <c r="B1121" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1122" spans="1:2" x14ac:dyDescent="0.2">
@@ -13532,7 +13538,7 @@
         <v>9062264</v>
       </c>
       <c r="B1122" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1123" spans="1:2" x14ac:dyDescent="0.2">
@@ -13540,7 +13546,7 @@
         <v>9062355</v>
       </c>
       <c r="B1123" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1124" spans="1:2" x14ac:dyDescent="0.2">
@@ -13548,7 +13554,7 @@
         <v>9062359</v>
       </c>
       <c r="B1124" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="1125" spans="1:2" x14ac:dyDescent="0.2">
@@ -13556,7 +13562,7 @@
         <v>9062363</v>
       </c>
       <c r="B1125" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1126" spans="1:2" x14ac:dyDescent="0.2">
@@ -13564,7 +13570,7 @@
         <v>9062373</v>
       </c>
       <c r="B1126" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="1127" spans="1:2" x14ac:dyDescent="0.2">
@@ -13572,7 +13578,7 @@
         <v>9062383</v>
       </c>
       <c r="B1127" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1128" spans="1:2" x14ac:dyDescent="0.2">
@@ -13580,7 +13586,7 @@
         <v>10248787</v>
       </c>
       <c r="B1128" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1129" spans="1:2" x14ac:dyDescent="0.2">
@@ -13588,7 +13594,7 @@
         <v>10248999</v>
       </c>
       <c r="B1129" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1130" spans="1:2" x14ac:dyDescent="0.2">
@@ -13596,7 +13602,7 @@
         <v>10249025</v>
       </c>
       <c r="B1130" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1131" spans="1:2" x14ac:dyDescent="0.2">
@@ -13604,7 +13610,7 @@
         <v>9002786</v>
       </c>
       <c r="B1131" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1132" spans="1:2" x14ac:dyDescent="0.2">
@@ -13612,7 +13618,7 @@
         <v>9002792</v>
       </c>
       <c r="B1132" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="1133" spans="1:2" x14ac:dyDescent="0.2">
@@ -13620,7 +13626,7 @@
         <v>9002808</v>
       </c>
       <c r="B1133" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1134" spans="1:2" x14ac:dyDescent="0.2">
@@ -13628,7 +13634,7 @@
         <v>9002814</v>
       </c>
       <c r="B1134" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1135" spans="1:2" x14ac:dyDescent="0.2">
@@ -13636,7 +13642,7 @@
         <v>10093373</v>
       </c>
       <c r="B1135" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1136" spans="1:2" x14ac:dyDescent="0.2">
@@ -13644,7 +13650,7 @@
         <v>9002822</v>
       </c>
       <c r="B1136" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1137" spans="1:2" x14ac:dyDescent="0.2">
@@ -13652,7 +13658,7 @@
         <v>9002828</v>
       </c>
       <c r="B1137" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1138" spans="1:2" x14ac:dyDescent="0.2">
@@ -13660,7 +13666,7 @@
         <v>9002842</v>
       </c>
       <c r="B1138" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1139" spans="1:2" x14ac:dyDescent="0.2">
@@ -13668,7 +13674,7 @@
         <v>9002849</v>
       </c>
       <c r="B1139" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1140" spans="1:2" x14ac:dyDescent="0.2">
@@ -13676,7 +13682,7 @@
         <v>9002860</v>
       </c>
       <c r="B1140" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1141" spans="1:2" x14ac:dyDescent="0.2">
@@ -13684,7 +13690,7 @@
         <v>9002871</v>
       </c>
       <c r="B1141" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1142" spans="1:2" x14ac:dyDescent="0.2">
@@ -13692,7 +13698,7 @@
         <v>9002888</v>
       </c>
       <c r="B1142" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1143" spans="1:2" x14ac:dyDescent="0.2">
@@ -13700,7 +13706,7 @@
         <v>9002900</v>
       </c>
       <c r="B1143" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1144" spans="1:2" x14ac:dyDescent="0.2">
@@ -13708,7 +13714,7 @@
         <v>9002904</v>
       </c>
       <c r="B1144" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1145" spans="1:2" x14ac:dyDescent="0.2">
@@ -13716,7 +13722,7 @@
         <v>9002927</v>
       </c>
       <c r="B1145" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1146" spans="1:2" x14ac:dyDescent="0.2">
@@ -13724,7 +13730,7 @@
         <v>9002937</v>
       </c>
       <c r="B1146" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1147" spans="1:2" x14ac:dyDescent="0.2">
@@ -13732,7 +13738,7 @@
         <v>10093723</v>
       </c>
       <c r="B1147" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1148" spans="1:2" x14ac:dyDescent="0.2">
@@ -13740,7 +13746,7 @@
         <v>9002944</v>
       </c>
       <c r="B1148" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1149" spans="1:2" x14ac:dyDescent="0.2">
@@ -13748,7 +13754,7 @@
         <v>9002958</v>
       </c>
       <c r="B1149" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1150" spans="1:2" x14ac:dyDescent="0.2">
@@ -13756,7 +13762,7 @@
         <v>9002964</v>
       </c>
       <c r="B1150" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1151" spans="1:2" x14ac:dyDescent="0.2">
@@ -13764,7 +13770,7 @@
         <v>9002980</v>
       </c>
       <c r="B1151" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1152" spans="1:2" x14ac:dyDescent="0.2">
@@ -13772,7 +13778,7 @@
         <v>9002986</v>
       </c>
       <c r="B1152" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1153" spans="1:2" x14ac:dyDescent="0.2">
@@ -13780,7 +13786,7 @@
         <v>10097367</v>
       </c>
       <c r="B1153" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1154" spans="1:2" x14ac:dyDescent="0.2">
@@ -13788,7 +13794,7 @@
         <v>9002994</v>
       </c>
       <c r="B1154" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1155" spans="1:2" x14ac:dyDescent="0.2">
@@ -13796,7 +13802,7 @@
         <v>9003000</v>
       </c>
       <c r="B1155" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1156" spans="1:2" x14ac:dyDescent="0.2">
@@ -13804,7 +13810,7 @@
         <v>9003014</v>
       </c>
       <c r="B1156" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1157" spans="1:2" x14ac:dyDescent="0.2">
@@ -13812,7 +13818,7 @@
         <v>9003021</v>
       </c>
       <c r="B1157" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1158" spans="1:2" x14ac:dyDescent="0.2">
@@ -13820,7 +13826,7 @@
         <v>9003033</v>
       </c>
       <c r="B1158" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1159" spans="1:2" x14ac:dyDescent="0.2">
@@ -13828,7 +13834,7 @@
         <v>9003044</v>
       </c>
       <c r="B1159" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1160" spans="1:2" x14ac:dyDescent="0.2">
@@ -13836,7 +13842,7 @@
         <v>9003061</v>
       </c>
       <c r="B1160" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="1161" spans="1:2" x14ac:dyDescent="0.2">
@@ -13844,7 +13850,7 @@
         <v>9003073</v>
       </c>
       <c r="B1161" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1162" spans="1:2" x14ac:dyDescent="0.2">
@@ -13852,7 +13858,7 @@
         <v>9003077</v>
       </c>
       <c r="B1162" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1163" spans="1:2" x14ac:dyDescent="0.2">
@@ -13860,7 +13866,7 @@
         <v>9003100</v>
       </c>
       <c r="B1163" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1164" spans="1:2" x14ac:dyDescent="0.2">
@@ -13868,7 +13874,7 @@
         <v>9003110</v>
       </c>
       <c r="B1164" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="1165" spans="1:2" x14ac:dyDescent="0.2">
@@ -13876,7 +13882,7 @@
         <v>10099237</v>
       </c>
       <c r="B1165" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1166" spans="1:2" x14ac:dyDescent="0.2">
@@ -13884,7 +13890,7 @@
         <v>9003117</v>
       </c>
       <c r="B1166" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="1167" spans="1:2" x14ac:dyDescent="0.2">
@@ -13892,7 +13898,7 @@
         <v>10099369</v>
       </c>
       <c r="B1167" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1168" spans="1:2" x14ac:dyDescent="0.2">
@@ -13900,7 +13906,7 @@
         <v>10099431</v>
       </c>
       <c r="B1168" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1169" spans="1:2" x14ac:dyDescent="0.2">
@@ -13908,7 +13914,7 @@
         <v>10099522</v>
       </c>
       <c r="B1169" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="1170" spans="1:2" x14ac:dyDescent="0.2">
@@ -13916,7 +13922,7 @@
         <v>10099529</v>
       </c>
       <c r="B1170" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1171" spans="1:2" x14ac:dyDescent="0.2">
@@ -13924,7 +13930,7 @@
         <v>10240774</v>
       </c>
       <c r="B1171" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1172" spans="1:2" x14ac:dyDescent="0.2">
@@ -13932,7 +13938,7 @@
         <v>10099536</v>
       </c>
       <c r="B1172" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="1173" spans="1:2" x14ac:dyDescent="0.2">
@@ -13940,7 +13946,7 @@
         <v>10099564</v>
       </c>
       <c r="B1173" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="1174" spans="1:2" x14ac:dyDescent="0.2">
@@ -13948,7 +13954,7 @@
         <v>10099592</v>
       </c>
       <c r="B1174" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="1175" spans="1:2" x14ac:dyDescent="0.2">
@@ -13956,7 +13962,7 @@
         <v>10099631</v>
       </c>
       <c r="B1175" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="1176" spans="1:2" x14ac:dyDescent="0.2">
@@ -13964,7 +13970,7 @@
         <v>10099696</v>
       </c>
       <c r="B1176" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="1177" spans="1:2" x14ac:dyDescent="0.2">
@@ -13972,7 +13978,7 @@
         <v>10099731</v>
       </c>
       <c r="B1177" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="1178" spans="1:2" x14ac:dyDescent="0.2">
@@ -13980,7 +13986,7 @@
         <v>10099743</v>
       </c>
       <c r="B1178" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="1179" spans="1:2" x14ac:dyDescent="0.2">
@@ -13988,7 +13994,7 @@
         <v>10099757</v>
       </c>
       <c r="B1179" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="1180" spans="1:2" x14ac:dyDescent="0.2">
@@ -13996,7 +14002,7 @@
         <v>10099790</v>
       </c>
       <c r="B1180" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="1181" spans="1:2" x14ac:dyDescent="0.2">
@@ -14004,7 +14010,7 @@
         <v>10099794</v>
       </c>
       <c r="B1181" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="1182" spans="1:2" x14ac:dyDescent="0.2">
@@ -14012,7 +14018,7 @@
         <v>10099829</v>
       </c>
       <c r="B1182" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="1183" spans="1:2" x14ac:dyDescent="0.2">
@@ -14020,7 +14026,7 @@
         <v>10099833</v>
       </c>
       <c r="B1183" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="1184" spans="1:2" x14ac:dyDescent="0.2">
@@ -14028,7 +14034,7 @@
         <v>10099837</v>
       </c>
       <c r="B1184" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.2">
@@ -14036,7 +14042,7 @@
         <v>10099901</v>
       </c>
       <c r="B1185" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="1186" spans="1:2" x14ac:dyDescent="0.2">
@@ -14044,7 +14050,7 @@
         <v>10099959</v>
       </c>
       <c r="B1186" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="1187" spans="1:2" x14ac:dyDescent="0.2">
@@ -14052,7 +14058,7 @@
         <v>10099968</v>
       </c>
       <c r="B1187" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="1188" spans="1:2" x14ac:dyDescent="0.2">
@@ -14060,7 +14066,7 @@
         <v>10240804</v>
       </c>
       <c r="B1188" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="1189" spans="1:2" x14ac:dyDescent="0.2">
@@ -14068,7 +14074,7 @@
         <v>10099985</v>
       </c>
       <c r="B1189" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="1190" spans="1:2" x14ac:dyDescent="0.2">
@@ -14076,7 +14082,7 @@
         <v>10100011</v>
       </c>
       <c r="B1190" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="1191" spans="1:2" x14ac:dyDescent="0.2">
@@ -14084,7 +14090,7 @@
         <v>10094951</v>
       </c>
       <c r="B1191" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="1192" spans="1:2" x14ac:dyDescent="0.2">
@@ -14092,7 +14098,7 @@
         <v>10094960</v>
       </c>
       <c r="B1192" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.2">
@@ -14100,7 +14106,7 @@
         <v>10094968</v>
       </c>
       <c r="B1193" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="1194" spans="1:2" x14ac:dyDescent="0.2">
@@ -14108,7 +14114,7 @@
         <v>10095017</v>
       </c>
       <c r="B1194" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="1195" spans="1:2" x14ac:dyDescent="0.2">
@@ -14116,7 +14122,7 @@
         <v>10095161</v>
       </c>
       <c r="B1195" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="1196" spans="1:2" x14ac:dyDescent="0.2">
@@ -14124,7 +14130,7 @@
         <v>10095170</v>
       </c>
       <c r="B1196" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.2">
@@ -14132,7 +14138,7 @@
         <v>9089394</v>
       </c>
       <c r="B1197" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="1198" spans="1:2" x14ac:dyDescent="0.2">
@@ -14140,7 +14146,7 @@
         <v>10095179</v>
       </c>
       <c r="B1198" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="1199" spans="1:2" x14ac:dyDescent="0.2">
@@ -14148,7 +14154,7 @@
         <v>9087840</v>
       </c>
       <c r="B1199" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="1200" spans="1:2" x14ac:dyDescent="0.2">
@@ -14156,7 +14162,7 @@
         <v>10095225</v>
       </c>
       <c r="B1200" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1201" spans="1:2" x14ac:dyDescent="0.2">
@@ -14164,7 +14170,7 @@
         <v>10095274</v>
       </c>
       <c r="B1201" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="1202" spans="1:2" x14ac:dyDescent="0.2">
@@ -14172,7 +14178,7 @@
         <v>10095328</v>
       </c>
       <c r="B1202" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="1203" spans="1:2" x14ac:dyDescent="0.2">
@@ -14180,7 +14186,7 @@
         <v>10095378</v>
       </c>
       <c r="B1203" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="1204" spans="1:2" x14ac:dyDescent="0.2">
@@ -14188,7 +14194,7 @@
         <v>10240710</v>
       </c>
       <c r="B1204" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="1205" spans="1:2" x14ac:dyDescent="0.2">
@@ -14196,7 +14202,7 @@
         <v>10095418</v>
       </c>
       <c r="B1205" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="1206" spans="1:2" x14ac:dyDescent="0.2">
@@ -14204,7 +14210,7 @@
         <v>10095533</v>
       </c>
       <c r="B1206" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="1207" spans="1:2" x14ac:dyDescent="0.2">
@@ -14212,7 +14218,7 @@
         <v>10095542</v>
       </c>
       <c r="B1207" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="1208" spans="1:2" x14ac:dyDescent="0.2">
@@ -14220,7 +14226,7 @@
         <v>10095551</v>
       </c>
       <c r="B1208" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="1209" spans="1:2" x14ac:dyDescent="0.2">
@@ -14228,7 +14234,7 @@
         <v>10095652</v>
       </c>
       <c r="B1209" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="1210" spans="1:2" x14ac:dyDescent="0.2">
@@ -14236,7 +14242,7 @@
         <v>10095665</v>
       </c>
       <c r="B1210" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="1211" spans="1:2" x14ac:dyDescent="0.2">
@@ -14244,7 +14250,7 @@
         <v>9048682</v>
       </c>
       <c r="B1211" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="1212" spans="1:2" x14ac:dyDescent="0.2">
@@ -14252,7 +14258,7 @@
         <v>10095678</v>
       </c>
       <c r="B1212" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.2">
@@ -14260,7 +14266,7 @@
         <v>10095814</v>
       </c>
       <c r="B1213" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="1214" spans="1:2" x14ac:dyDescent="0.2">
@@ -14268,7 +14274,7 @@
         <v>10095972</v>
       </c>
       <c r="B1214" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="1215" spans="1:2" x14ac:dyDescent="0.2">
@@ -14276,7 +14282,7 @@
         <v>10095976</v>
       </c>
       <c r="B1215" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="1216" spans="1:2" x14ac:dyDescent="0.2">
@@ -14284,7 +14290,7 @@
         <v>10095980</v>
       </c>
       <c r="B1216" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="1217" spans="1:2" x14ac:dyDescent="0.2">
@@ -14292,7 +14298,7 @@
         <v>10095984</v>
       </c>
       <c r="B1217" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="1218" spans="1:2" x14ac:dyDescent="0.2">
@@ -14300,7 +14306,7 @@
         <v>10096254</v>
       </c>
       <c r="B1218" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="1219" spans="1:2" x14ac:dyDescent="0.2">
@@ -14308,7 +14314,7 @@
         <v>10096268</v>
       </c>
       <c r="B1219" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="1220" spans="1:2" x14ac:dyDescent="0.2">
@@ -14316,7 +14322,7 @@
         <v>10096311</v>
       </c>
       <c r="B1220" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="1221" spans="1:2" x14ac:dyDescent="0.2">
@@ -14324,7 +14330,7 @@
         <v>10096433</v>
       </c>
       <c r="B1221" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="1222" spans="1:2" x14ac:dyDescent="0.2">
@@ -14332,7 +14338,7 @@
         <v>10096471</v>
       </c>
       <c r="B1222" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="1223" spans="1:2" x14ac:dyDescent="0.2">
@@ -14340,7 +14346,7 @@
         <v>10096575</v>
       </c>
       <c r="B1223" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="1224" spans="1:2" x14ac:dyDescent="0.2">
@@ -14348,7 +14354,7 @@
         <v>10096652</v>
       </c>
       <c r="B1224" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.2">
@@ -14356,7 +14362,7 @@
         <v>10096718</v>
       </c>
       <c r="B1225" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="1226" spans="1:2" x14ac:dyDescent="0.2">
@@ -14364,7 +14370,7 @@
         <v>10192432</v>
       </c>
       <c r="B1226" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="1227" spans="1:2" x14ac:dyDescent="0.2">
@@ -14372,7 +14378,7 @@
         <v>10192458</v>
       </c>
       <c r="B1227" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="1228" spans="1:2" x14ac:dyDescent="0.2">
@@ -14380,7 +14386,7 @@
         <v>10192490</v>
       </c>
       <c r="B1228" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="1229" spans="1:2" x14ac:dyDescent="0.2">
@@ -14388,7 +14394,7 @@
         <v>10192497</v>
       </c>
       <c r="B1229" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="1230" spans="1:2" x14ac:dyDescent="0.2">
@@ -14396,7 +14402,7 @@
         <v>10113606</v>
       </c>
       <c r="B1230" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="1231" spans="1:2" x14ac:dyDescent="0.2">
@@ -14404,7 +14410,7 @@
         <v>10113612</v>
       </c>
       <c r="B1231" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="1232" spans="1:2" x14ac:dyDescent="0.2">
@@ -14412,7 +14418,7 @@
         <v>10113649</v>
       </c>
       <c r="B1232" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="1233" spans="1:2" x14ac:dyDescent="0.2">
@@ -14420,7 +14426,7 @@
         <v>10192511</v>
       </c>
       <c r="B1233" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="1234" spans="1:2" x14ac:dyDescent="0.2">
@@ -14428,7 +14434,7 @@
         <v>10113654</v>
       </c>
       <c r="B1234" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="1235" spans="1:2" x14ac:dyDescent="0.2">
@@ -14436,7 +14442,7 @@
         <v>10113696</v>
       </c>
       <c r="B1235" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="1236" spans="1:2" x14ac:dyDescent="0.2">
@@ -14444,7 +14450,7 @@
         <v>10113723</v>
       </c>
       <c r="B1236" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="1237" spans="1:2" x14ac:dyDescent="0.2">
@@ -14452,7 +14458,7 @@
         <v>10113729</v>
       </c>
       <c r="B1237" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="1238" spans="1:2" x14ac:dyDescent="0.2">
@@ -14460,7 +14466,7 @@
         <v>10113771</v>
       </c>
       <c r="B1238" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="1239" spans="1:2" x14ac:dyDescent="0.2">
@@ -14468,7 +14474,7 @@
         <v>10113858</v>
       </c>
       <c r="B1239" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="1240" spans="1:2" x14ac:dyDescent="0.2">
@@ -14476,7 +14482,7 @@
         <v>10113913</v>
       </c>
       <c r="B1240" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="1241" spans="1:2" x14ac:dyDescent="0.2">
@@ -14484,7 +14490,7 @@
         <v>9061939</v>
       </c>
       <c r="B1241" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="1242" spans="1:2" x14ac:dyDescent="0.2">
@@ -14492,7 +14498,7 @@
         <v>9053419</v>
       </c>
       <c r="B1242" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="1243" spans="1:2" x14ac:dyDescent="0.2">
@@ -14500,7 +14506,7 @@
         <v>9061909</v>
       </c>
       <c r="B1243" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="1244" spans="1:2" x14ac:dyDescent="0.2">
@@ -14508,7 +14514,7 @@
         <v>10113985</v>
       </c>
       <c r="B1244" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="1245" spans="1:2" x14ac:dyDescent="0.2">
@@ -14516,7 +14522,7 @@
         <v>10114041</v>
       </c>
       <c r="B1245" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="1246" spans="1:2" x14ac:dyDescent="0.2">
@@ -14524,7 +14530,7 @@
         <v>10114046</v>
       </c>
       <c r="B1246" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="1247" spans="1:2" x14ac:dyDescent="0.2">
@@ -14532,7 +14538,7 @@
         <v>10114068</v>
       </c>
       <c r="B1247" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="1248" spans="1:2" x14ac:dyDescent="0.2">
@@ -14540,7 +14546,7 @@
         <v>9116725</v>
       </c>
       <c r="B1248" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="1249" spans="1:2" x14ac:dyDescent="0.2">
@@ -14548,7 +14554,7 @@
         <v>10219012</v>
       </c>
       <c r="B1249" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="1250" spans="1:2" x14ac:dyDescent="0.2">
@@ -14556,7 +14562,7 @@
         <v>10219021</v>
       </c>
       <c r="B1250" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="1251" spans="1:2" x14ac:dyDescent="0.2">
@@ -14564,7 +14570,7 @@
         <v>10219139</v>
       </c>
       <c r="B1251" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="1252" spans="1:2" x14ac:dyDescent="0.2">
@@ -14572,7 +14578,7 @@
         <v>10219146</v>
       </c>
       <c r="B1252" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="1253" spans="1:2" x14ac:dyDescent="0.2">
@@ -14580,7 +14586,7 @@
         <v>10219241</v>
       </c>
       <c r="B1253" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="1254" spans="1:2" x14ac:dyDescent="0.2">
@@ -14588,7 +14594,7 @@
         <v>10219248</v>
       </c>
       <c r="B1254" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="1255" spans="1:2" x14ac:dyDescent="0.2">
@@ -14596,7 +14602,7 @@
         <v>10219255</v>
       </c>
       <c r="B1255" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="1256" spans="1:2" x14ac:dyDescent="0.2">
@@ -14604,7 +14610,7 @@
         <v>10219369</v>
       </c>
       <c r="B1256" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="1257" spans="1:2" x14ac:dyDescent="0.2">
@@ -14612,7 +14618,7 @@
         <v>10219376</v>
       </c>
       <c r="B1257" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="1258" spans="1:2" x14ac:dyDescent="0.2">
@@ -14620,7 +14626,7 @@
         <v>9093923</v>
       </c>
       <c r="B1258" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="1259" spans="1:2" x14ac:dyDescent="0.2">
@@ -14628,7 +14634,7 @@
         <v>10219383</v>
       </c>
       <c r="B1259" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="1260" spans="1:2" x14ac:dyDescent="0.2">
@@ -14636,7 +14642,7 @@
         <v>10219455</v>
       </c>
       <c r="B1260" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="1261" spans="1:2" x14ac:dyDescent="0.2">
@@ -14644,7 +14650,7 @@
         <v>10219462</v>
       </c>
       <c r="B1261" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="1262" spans="1:2" x14ac:dyDescent="0.2">
@@ -14652,7 +14658,7 @@
         <v>10219469</v>
       </c>
       <c r="B1262" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="1263" spans="1:2" x14ac:dyDescent="0.2">
@@ -14660,7 +14666,7 @@
         <v>10219564</v>
       </c>
       <c r="B1263" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="1264" spans="1:2" x14ac:dyDescent="0.2">
@@ -14668,7 +14674,7 @@
         <v>10219675</v>
       </c>
       <c r="B1264" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="1265" spans="1:2" x14ac:dyDescent="0.2">
@@ -14676,7 +14682,7 @@
         <v>10219745</v>
       </c>
       <c r="B1265" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="1266" spans="1:2" x14ac:dyDescent="0.2">
@@ -14684,7 +14690,7 @@
         <v>10219794</v>
       </c>
       <c r="B1266" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="1267" spans="1:2" x14ac:dyDescent="0.2">
@@ -14692,7 +14698,7 @@
         <v>10219887</v>
       </c>
       <c r="B1267" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="1268" spans="1:2" x14ac:dyDescent="0.2">
@@ -14700,7 +14706,7 @@
         <v>10219891</v>
       </c>
       <c r="B1268" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1269" spans="1:2" x14ac:dyDescent="0.2">
@@ -14708,7 +14714,7 @@
         <v>10220174</v>
       </c>
       <c r="B1269" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="1270" spans="1:2" x14ac:dyDescent="0.2">
@@ -14716,7 +14722,7 @@
         <v>10220237</v>
       </c>
       <c r="B1270" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="1271" spans="1:2" x14ac:dyDescent="0.2">
@@ -14724,7 +14730,7 @@
         <v>10220265</v>
       </c>
       <c r="B1271" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="1272" spans="1:2" x14ac:dyDescent="0.2">
@@ -14732,7 +14738,7 @@
         <v>10220369</v>
       </c>
       <c r="B1272" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.2">
@@ -14740,7 +14746,7 @@
         <v>9057498</v>
       </c>
       <c r="B1273" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1274" spans="1:2" x14ac:dyDescent="0.2">
@@ -14748,7 +14754,7 @@
         <v>9057522</v>
       </c>
       <c r="B1274" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.2">
@@ -14756,7 +14762,7 @@
         <v>10111370</v>
       </c>
       <c r="B1275" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="1276" spans="1:2" x14ac:dyDescent="0.2">
@@ -14764,7 +14770,7 @@
         <v>9057557</v>
       </c>
       <c r="B1276" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="1277" spans="1:2" x14ac:dyDescent="0.2">
@@ -14772,7 +14778,7 @@
         <v>9057679</v>
       </c>
       <c r="B1277" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1278" spans="1:2" x14ac:dyDescent="0.2">
@@ -14780,7 +14786,7 @@
         <v>10111378</v>
       </c>
       <c r="B1278" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1279" spans="1:2" x14ac:dyDescent="0.2">
@@ -14788,7 +14794,7 @@
         <v>10111518</v>
       </c>
       <c r="B1279" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1280" spans="1:2" x14ac:dyDescent="0.2">
@@ -14796,7 +14802,7 @@
         <v>9057741</v>
       </c>
       <c r="B1280" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1281" spans="1:2" x14ac:dyDescent="0.2">
@@ -14804,7 +14810,7 @@
         <v>10111526</v>
       </c>
       <c r="B1281" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="1282" spans="1:2" x14ac:dyDescent="0.2">
@@ -14812,7 +14818,7 @@
         <v>10111666</v>
       </c>
       <c r="B1282" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.2">
@@ -14820,7 +14826,7 @@
         <v>10111755</v>
       </c>
       <c r="B1283" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="1284" spans="1:2" x14ac:dyDescent="0.2">
@@ -14828,7 +14834,7 @@
         <v>10111763</v>
       </c>
       <c r="B1284" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1285" spans="1:2" x14ac:dyDescent="0.2">
@@ -14836,7 +14842,7 @@
         <v>10111838</v>
       </c>
       <c r="B1285" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1286" spans="1:2" x14ac:dyDescent="0.2">
@@ -14844,7 +14850,7 @@
         <v>10111939</v>
       </c>
       <c r="B1286" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1287" spans="1:2" x14ac:dyDescent="0.2">
@@ -14852,7 +14858,7 @@
         <v>10111994</v>
       </c>
       <c r="B1287" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="1288" spans="1:2" x14ac:dyDescent="0.2">
@@ -14860,7 +14866,7 @@
         <v>9057452</v>
       </c>
       <c r="B1288" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="1289" spans="1:2" x14ac:dyDescent="0.2">
@@ -14868,7 +14874,7 @@
         <v>9053424</v>
       </c>
       <c r="B1289" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1290" spans="1:2" x14ac:dyDescent="0.2">
@@ -14876,7 +14882,7 @@
         <v>10112171</v>
       </c>
       <c r="B1290" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="1291" spans="1:2" x14ac:dyDescent="0.2">
@@ -14884,7 +14890,7 @@
         <v>9061541</v>
       </c>
       <c r="B1291" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="1292" spans="1:2" x14ac:dyDescent="0.2">
@@ -14892,7 +14898,7 @@
         <v>10112649</v>
       </c>
       <c r="B1292" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="1293" spans="1:2" x14ac:dyDescent="0.2">
@@ -14900,7 +14906,7 @@
         <v>10112656</v>
       </c>
       <c r="B1293" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1294" spans="1:2" x14ac:dyDescent="0.2">
@@ -14908,7 +14914,7 @@
         <v>10112720</v>
       </c>
       <c r="B1294" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="1295" spans="1:2" x14ac:dyDescent="0.2">
@@ -14916,7 +14922,7 @@
         <v>9116749</v>
       </c>
       <c r="B1295" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="1296" spans="1:2" x14ac:dyDescent="0.2">
@@ -14924,7 +14930,7 @@
         <v>10222126</v>
       </c>
       <c r="B1296" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="1297" spans="1:2" x14ac:dyDescent="0.2">
@@ -14932,7 +14938,7 @@
         <v>10222135</v>
       </c>
       <c r="B1297" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="1298" spans="1:2" x14ac:dyDescent="0.2">
@@ -14940,7 +14946,7 @@
         <v>10222245</v>
       </c>
       <c r="B1298" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1299" spans="1:2" x14ac:dyDescent="0.2">
@@ -14948,7 +14954,7 @@
         <v>10222252</v>
       </c>
       <c r="B1299" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="1300" spans="1:2" x14ac:dyDescent="0.2">
@@ -14956,7 +14962,7 @@
         <v>10222338</v>
       </c>
       <c r="B1300" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="1301" spans="1:2" x14ac:dyDescent="0.2">
@@ -14964,7 +14970,7 @@
         <v>10222345</v>
       </c>
       <c r="B1301" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="1302" spans="1:2" x14ac:dyDescent="0.2">
@@ -14972,7 +14978,7 @@
         <v>10222352</v>
       </c>
       <c r="B1302" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="1303" spans="1:2" x14ac:dyDescent="0.2">
@@ -14980,7 +14986,7 @@
         <v>10222472</v>
       </c>
       <c r="B1303" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="1304" spans="1:2" x14ac:dyDescent="0.2">
@@ -14988,7 +14994,7 @@
         <v>10222478</v>
       </c>
       <c r="B1304" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="1305" spans="1:2" x14ac:dyDescent="0.2">
@@ -14996,7 +15002,7 @@
         <v>10222484</v>
       </c>
       <c r="B1305" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="1306" spans="1:2" x14ac:dyDescent="0.2">
@@ -15004,7 +15010,7 @@
         <v>10222566</v>
       </c>
       <c r="B1306" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="1307" spans="1:2" x14ac:dyDescent="0.2">
@@ -15012,7 +15018,7 @@
         <v>10222574</v>
       </c>
       <c r="B1307" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="1308" spans="1:2" x14ac:dyDescent="0.2">
@@ -15020,7 +15026,7 @@
         <v>10222581</v>
       </c>
       <c r="B1308" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="1309" spans="1:2" x14ac:dyDescent="0.2">
@@ -15028,7 +15034,7 @@
         <v>10224616</v>
       </c>
       <c r="B1309" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1310" spans="1:2" x14ac:dyDescent="0.2">
@@ -15036,7 +15042,7 @@
         <v>10224718</v>
       </c>
       <c r="B1310" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="1311" spans="1:2" x14ac:dyDescent="0.2">
@@ -15044,7 +15050,7 @@
         <v>10224791</v>
       </c>
       <c r="B1311" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="1312" spans="1:2" x14ac:dyDescent="0.2">
@@ -15052,7 +15058,7 @@
         <v>10224835</v>
       </c>
       <c r="B1312" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="1313" spans="1:2" x14ac:dyDescent="0.2">
@@ -15060,7 +15066,7 @@
         <v>10224938</v>
       </c>
       <c r="B1313" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="1314" spans="1:2" x14ac:dyDescent="0.2">
@@ -15068,7 +15074,7 @@
         <v>10224941</v>
       </c>
       <c r="B1314" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="1315" spans="1:2" x14ac:dyDescent="0.2">
@@ -15076,7 +15082,7 @@
         <v>10240951</v>
       </c>
       <c r="B1315" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="1316" spans="1:2" x14ac:dyDescent="0.2">
@@ -15084,7 +15090,7 @@
         <v>10225214</v>
       </c>
       <c r="B1316" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1317" spans="1:2" x14ac:dyDescent="0.2">
@@ -15092,7 +15098,7 @@
         <v>10225274</v>
       </c>
       <c r="B1317" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="1318" spans="1:2" x14ac:dyDescent="0.2">
@@ -15100,7 +15106,7 @@
         <v>10225303</v>
       </c>
       <c r="B1318" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="1319" spans="1:2" x14ac:dyDescent="0.2">
@@ -15108,7 +15114,7 @@
         <v>10225388</v>
       </c>
       <c r="B1319" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="1320" spans="1:2" x14ac:dyDescent="0.2">
@@ -15116,7 +15122,7 @@
         <v>10135369</v>
       </c>
       <c r="B1320" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="1321" spans="1:2" x14ac:dyDescent="0.2">
@@ -15124,7 +15130,7 @@
         <v>10177256</v>
       </c>
       <c r="B1321" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="1322" spans="1:2" x14ac:dyDescent="0.2">
@@ -15132,7 +15138,7 @@
         <v>10135458</v>
       </c>
       <c r="B1322" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="1323" spans="1:2" x14ac:dyDescent="0.2">
@@ -15140,7 +15146,7 @@
         <v>10177300</v>
       </c>
       <c r="B1323" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="1324" spans="1:2" x14ac:dyDescent="0.2">
@@ -15148,7 +15154,7 @@
         <v>10135465</v>
       </c>
       <c r="B1324" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="1325" spans="1:2" x14ac:dyDescent="0.2">
@@ -15156,7 +15162,7 @@
         <v>9099732</v>
       </c>
       <c r="B1325" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="1326" spans="1:2" x14ac:dyDescent="0.2">
@@ -15164,7 +15170,7 @@
         <v>10177315</v>
       </c>
       <c r="B1326" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="1327" spans="1:2" x14ac:dyDescent="0.2">
@@ -15172,7 +15178,7 @@
         <v>10135513</v>
       </c>
       <c r="B1327" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="1328" spans="1:2" x14ac:dyDescent="0.2">
@@ -15180,7 +15186,7 @@
         <v>10135575</v>
       </c>
       <c r="B1328" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="1329" spans="1:2" x14ac:dyDescent="0.2">
@@ -15188,7 +15194,7 @@
         <v>10135682</v>
       </c>
       <c r="B1329" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.2">
@@ -15196,7 +15202,7 @@
         <v>10135748</v>
       </c>
       <c r="B1330" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="1331" spans="1:2" x14ac:dyDescent="0.2">
@@ -15204,7 +15210,7 @@
         <v>10135755</v>
       </c>
       <c r="B1331" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="1332" spans="1:2" x14ac:dyDescent="0.2">
@@ -15212,7 +15218,7 @@
         <v>10177573</v>
       </c>
       <c r="B1332" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="1333" spans="1:2" x14ac:dyDescent="0.2">
@@ -15220,7 +15226,7 @@
         <v>10177599</v>
       </c>
       <c r="B1333" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="1334" spans="1:2" x14ac:dyDescent="0.2">
@@ -15228,7 +15234,7 @@
         <v>10177347</v>
       </c>
       <c r="B1334" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="1335" spans="1:2" x14ac:dyDescent="0.2">
@@ -15236,7 +15242,7 @@
         <v>10177441</v>
       </c>
       <c r="B1335" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="1336" spans="1:2" x14ac:dyDescent="0.2">
@@ -15244,7 +15250,7 @@
         <v>9099729</v>
       </c>
       <c r="B1336" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="1337" spans="1:2" x14ac:dyDescent="0.2">
@@ -15252,7 +15258,7 @@
         <v>10177484</v>
       </c>
       <c r="B1337" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="1338" spans="1:2" x14ac:dyDescent="0.2">
@@ -15260,7 +15266,7 @@
         <v>10177490</v>
       </c>
       <c r="B1338" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="1339" spans="1:2" x14ac:dyDescent="0.2">
@@ -15268,7 +15274,7 @@
         <v>10135588</v>
       </c>
       <c r="B1339" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="1340" spans="1:2" x14ac:dyDescent="0.2">
@@ -15276,7 +15282,7 @@
         <v>9094511</v>
       </c>
       <c r="B1340" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="1341" spans="1:2" x14ac:dyDescent="0.2">
@@ -15284,7 +15290,7 @@
         <v>9056503</v>
       </c>
       <c r="B1341" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="1342" spans="1:2" x14ac:dyDescent="0.2">
@@ -15292,7 +15298,7 @@
         <v>10135949</v>
       </c>
       <c r="B1342" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1343" spans="1:2" x14ac:dyDescent="0.2">
@@ -15300,7 +15306,7 @@
         <v>9056513</v>
       </c>
       <c r="B1343" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="1344" spans="1:2" x14ac:dyDescent="0.2">
@@ -15308,7 +15314,7 @@
         <v>10211408</v>
       </c>
       <c r="B1344" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="1345" spans="1:2" x14ac:dyDescent="0.2">
@@ -15316,7 +15322,7 @@
         <v>10136103</v>
       </c>
       <c r="B1345" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="1346" spans="1:2" x14ac:dyDescent="0.2">
@@ -15324,7 +15330,7 @@
         <v>10211413</v>
       </c>
       <c r="B1346" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="1347" spans="1:2" x14ac:dyDescent="0.2">
@@ -15332,7 +15338,7 @@
         <v>10211422</v>
       </c>
       <c r="B1347" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="1348" spans="1:2" x14ac:dyDescent="0.2">
@@ -15340,7 +15346,7 @@
         <v>10136159</v>
       </c>
       <c r="B1348" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="1349" spans="1:2" x14ac:dyDescent="0.2">
@@ -15348,7 +15354,7 @@
         <v>9056535</v>
       </c>
       <c r="B1349" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="1350" spans="1:2" x14ac:dyDescent="0.2">
@@ -15356,7 +15362,7 @@
         <v>10136290</v>
       </c>
       <c r="B1350" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="1351" spans="1:2" x14ac:dyDescent="0.2">
@@ -15364,7 +15370,7 @@
         <v>9056612</v>
       </c>
       <c r="B1351" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="1352" spans="1:2" x14ac:dyDescent="0.2">
@@ -15372,7 +15378,7 @@
         <v>10211427</v>
       </c>
       <c r="B1352" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="1353" spans="1:2" x14ac:dyDescent="0.2">
@@ -15380,7 +15386,7 @@
         <v>10136447</v>
       </c>
       <c r="B1353" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="1354" spans="1:2" x14ac:dyDescent="0.2">
@@ -15388,7 +15394,7 @@
         <v>10136476</v>
       </c>
       <c r="B1354" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="1355" spans="1:2" x14ac:dyDescent="0.2">
@@ -15396,7 +15402,7 @@
         <v>10136635</v>
       </c>
       <c r="B1355" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="1356" spans="1:2" x14ac:dyDescent="0.2">
@@ -15404,7 +15410,7 @@
         <v>10136642</v>
       </c>
       <c r="B1356" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="1357" spans="1:2" x14ac:dyDescent="0.2">
@@ -15412,7 +15418,7 @@
         <v>9056782</v>
       </c>
       <c r="B1357" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="1358" spans="1:2" x14ac:dyDescent="0.2">
@@ -15420,7 +15426,7 @@
         <v>9111957</v>
       </c>
       <c r="B1358" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="1359" spans="1:2" x14ac:dyDescent="0.2">
@@ -15428,7 +15434,7 @@
         <v>10211475</v>
       </c>
       <c r="B1359" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="1360" spans="1:2" x14ac:dyDescent="0.2">
@@ -15436,7 +15442,7 @@
         <v>9056809</v>
       </c>
       <c r="B1360" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="1361" spans="1:2" x14ac:dyDescent="0.2">
@@ -15444,7 +15450,7 @@
         <v>10136719</v>
       </c>
       <c r="B1361" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="1362" spans="1:2" x14ac:dyDescent="0.2">
@@ -15452,7 +15458,7 @@
         <v>9088988</v>
       </c>
       <c r="B1362" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="1363" spans="1:2" x14ac:dyDescent="0.2">
@@ -15460,7 +15466,7 @@
         <v>9124613</v>
       </c>
       <c r="B1363" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="1364" spans="1:2" x14ac:dyDescent="0.2">
@@ -15468,7 +15474,7 @@
         <v>10136898</v>
       </c>
       <c r="B1364" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="1365" spans="1:2" x14ac:dyDescent="0.2">
@@ -15476,7 +15482,7 @@
         <v>10093859</v>
       </c>
       <c r="B1365" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="1366" spans="1:2" x14ac:dyDescent="0.2">
@@ -15484,7 +15490,7 @@
         <v>10093955</v>
       </c>
       <c r="B1366" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="1367" spans="1:2" x14ac:dyDescent="0.2">
@@ -15492,7 +15498,7 @@
         <v>10115949</v>
       </c>
       <c r="B1367" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="1368" spans="1:2" x14ac:dyDescent="0.2">
@@ -15500,7 +15506,7 @@
         <v>9063904</v>
       </c>
       <c r="B1368" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="1369" spans="1:2" x14ac:dyDescent="0.2">
@@ -15508,7 +15514,7 @@
         <v>10209721</v>
       </c>
       <c r="B1369" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="1370" spans="1:2" x14ac:dyDescent="0.2">
@@ -15516,7 +15522,7 @@
         <v>10228719</v>
       </c>
       <c r="B1370" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="1371" spans="1:2" x14ac:dyDescent="0.2">
@@ -15524,7 +15530,7 @@
         <v>10228774</v>
       </c>
       <c r="B1371" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="1372" spans="1:2" x14ac:dyDescent="0.2">
@@ -15532,7 +15538,7 @@
         <v>10228794</v>
       </c>
       <c r="B1372" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="1373" spans="1:2" x14ac:dyDescent="0.2">
@@ -15540,7 +15546,7 @@
         <v>10228846</v>
       </c>
       <c r="B1373" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="1374" spans="1:2" x14ac:dyDescent="0.2">
@@ -15548,7 +15554,7 @@
         <v>10248616</v>
       </c>
       <c r="B1374" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="1375" spans="1:2" x14ac:dyDescent="0.2">
@@ -15556,7 +15562,7 @@
         <v>10248637</v>
       </c>
       <c r="B1375" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="1376" spans="1:2" x14ac:dyDescent="0.2">
@@ -15564,7 +15570,7 @@
         <v>10248660</v>
       </c>
       <c r="B1376" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="1377" spans="1:2" x14ac:dyDescent="0.2">
@@ -15572,7 +15578,7 @@
         <v>10208995</v>
       </c>
       <c r="B1377" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="1378" spans="1:2" x14ac:dyDescent="0.2">
@@ -15580,7 +15586,7 @@
         <v>9112110</v>
       </c>
       <c r="B1378" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="1379" spans="1:2" x14ac:dyDescent="0.2">
@@ -15588,7 +15594,7 @@
         <v>10136841</v>
       </c>
       <c r="B1379" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="1380" spans="1:2" x14ac:dyDescent="0.2">
@@ -15596,7 +15602,7 @@
         <v>9873533</v>
       </c>
       <c r="B1380" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="1381" spans="1:2" x14ac:dyDescent="0.2">
@@ -15604,7 +15610,7 @@
         <v>9875531</v>
       </c>
       <c r="B1381" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="1382" spans="1:2" x14ac:dyDescent="0.2">
@@ -15612,7 +15618,7 @@
         <v>9048471</v>
       </c>
       <c r="B1382" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="1383" spans="1:2" x14ac:dyDescent="0.2">
@@ -15620,7 +15626,15 @@
         <v>9048481</v>
       </c>
       <c r="B1383" t="s">
-        <v>1381</v>
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1384">
+        <v>9999</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>1383</v>
       </c>
     </row>
   </sheetData>
